--- a/task139/golden/ern_placement_ay2027.xlsx
+++ b/task139/golden/ern_placement_ay2027.xlsx
@@ -199,7 +199,7 @@
     <t>Amounts: Kellerman Pryce's verified ultimate indemnity at 30 June 2026, no trend. Indemnity only.</t>
   </si>
   <si>
-    <t>2025 intakes: claims whose first report recorded time lost (charter 4.1), disability_began on or before report_date as the data dictionary defines it; on claims converted at the June 2025 upgrade time_off_at_report holds the legacy LOST_TIME indicator, so their dates decide. A claim listed twice from the 29 May to 1 June 2025 parallel run is counted once.</t>
+    <t>2025 intakes: claims whose first report recorded time lost (charter 4.1), disability_began on or before report_date as the data dictionary defines it; on claims converted at the June 2025 upgrade time_off_at_report holds the legacy LOST_TIME indicator, so their dates decide. A claim listed twice from the 29 May to 1 June 2025 parallel run is counted once, and a claim merged into another claim (claim_merges_2025.csv) counts with that claim.</t>
   </si>
   <si>
     <t>Indemnity paid: the payment register repeats a payment's amount on each weekly line, so each payment is counted once; voided checks and the EFTs in the bank's return file are left out.</t>
